--- a/data/attendance/AMPHI_زهراوي_علمي_1.xlsx
+++ b/data/attendance/AMPHI_زهراوي_علمي_1.xlsx
@@ -136,7 +136,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="36">
   <si>
-    <t>زهراوي علمي 1  |  AMPHI  |  BAC  |  - زهراوي</t>
+    <t>زهراوي علمي 1  |  AMPHI  |  BAC  |  زهراوي</t>
   </si>
   <si>
     <t>class_id=11</t>

--- a/data/attendance/AMPHI_زهراوي_علمي_1.xlsx
+++ b/data/attendance/AMPHI_زهراوي_علمي_1.xlsx
@@ -20,112 +20,154 @@
     <comment ref="B5" authorId="0">
       <text>
         <r>
-          <t>student_id:7ff636c7-eb84-41fd-b72a-0a38493ed2f3</t>
+          <t>student_id:5105aca6-6857-4a31-ab24-c9f3f7b3612b</t>
         </r>
       </text>
     </comment>
     <comment ref="B6" authorId="0">
       <text>
         <r>
-          <t>student_id:31faf3bc-d372-44fc-a439-1dad020ef211</t>
+          <t>student_id:a00b5e0f-4b92-4a58-ad0a-f851b10286b7</t>
         </r>
       </text>
     </comment>
     <comment ref="B7" authorId="0">
       <text>
         <r>
-          <t>student_id:a52a0329-b6e5-4dfd-8ef7-6d6bfc4a3e46</t>
+          <t>student_id:62f8dbea-d839-4620-852b-c61095b6129a</t>
         </r>
       </text>
     </comment>
     <comment ref="B8" authorId="0">
       <text>
         <r>
-          <t>student_id:519c7bc6-fee1-4125-a588-89e7d5c257b4</t>
+          <t>student_id:a9f2b729-1881-4aa9-8b7f-c010c77d6ff9</t>
         </r>
       </text>
     </comment>
     <comment ref="B9" authorId="0">
       <text>
         <r>
-          <t>student_id:098b4e1f-0b8a-4ac1-a406-4f05c8fda451</t>
+          <t>student_id:f9665799-bcdd-42cb-9ee2-2c0b46fad4a7</t>
         </r>
       </text>
     </comment>
     <comment ref="B10" authorId="0">
       <text>
         <r>
-          <t>student_id:bcaf02ed-8e33-44b8-821a-3204467f5a89</t>
+          <t>student_id:beb5a9b5-ace2-4d8c-8fa8-13d95aaf14b2</t>
         </r>
       </text>
     </comment>
     <comment ref="B11" authorId="0">
       <text>
         <r>
-          <t>student_id:6c5abb5e-b23d-4e84-bfec-962176b789ce</t>
+          <t>student_id:9b9aff36-6a0b-434b-ad5d-59c60712d22b</t>
         </r>
       </text>
     </comment>
     <comment ref="B12" authorId="0">
       <text>
         <r>
-          <t>student_id:a3849ee5-4407-4ce7-a3b9-d98d4a9ff0f1</t>
+          <t>student_id:30e3101c-0da1-45b4-ac64-04627e553de6</t>
         </r>
       </text>
     </comment>
     <comment ref="B13" authorId="0">
       <text>
         <r>
-          <t>student_id:269db174-b663-4c11-b918-0a9573e0c3ac</t>
+          <t>student_id:9480e9ce-8e6d-4576-81ec-49d56fd56037</t>
         </r>
       </text>
     </comment>
     <comment ref="B14" authorId="0">
       <text>
         <r>
-          <t>student_id:6527db96-d9e2-4272-953d-c99c1b53e0b2</t>
+          <t>student_id:5c4e15c8-f573-4322-ad01-86920db813a5</t>
         </r>
       </text>
     </comment>
     <comment ref="B15" authorId="0">
       <text>
         <r>
-          <t>student_id:4ba9d769-df8e-4dd1-8987-cb594a9711ff</t>
+          <t>student_id:74d856fa-0759-40be-8901-05a9e9c0add7</t>
         </r>
       </text>
     </comment>
     <comment ref="B16" authorId="0">
       <text>
         <r>
-          <t>student_id:0a7b9208-655a-4e1c-ba7a-3bde6d2e217a</t>
+          <t>student_id:2a443aed-c07a-4324-9e86-72a882fc64a8</t>
         </r>
       </text>
     </comment>
     <comment ref="B17" authorId="0">
       <text>
         <r>
-          <t>student_id:5e8609ef-8950-44af-9dd7-eb8a568ee133</t>
+          <t>student_id:069184e6-7edb-4d5d-b591-5b660f8d0159</t>
         </r>
       </text>
     </comment>
     <comment ref="B18" authorId="0">
       <text>
         <r>
-          <t>student_id:53e9ed69-38ba-4d5b-9eac-84eb15c5796b</t>
+          <t>student_id:e37c1325-4b0d-41a1-918b-2622eac4a0da</t>
         </r>
       </text>
     </comment>
     <comment ref="B19" authorId="0">
       <text>
         <r>
-          <t>student_id:53dce42a-d8c1-49f2-8a0e-ef24a0d1410a</t>
+          <t>student_id:4c2f9380-3065-42fe-852f-ac7919272b9a</t>
         </r>
       </text>
     </comment>
     <comment ref="B20" authorId="0">
       <text>
         <r>
-          <t>student_id:0ce53dbd-a2c7-49ae-8bd4-f77636a6db86</t>
+          <t>student_id:4578980d-ce40-4241-a7f9-008902aa677c</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B21" authorId="0">
+      <text>
+        <r>
+          <t>student_id:3190f13f-dec8-40a7-9922-9bad9efee130</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B22" authorId="0">
+      <text>
+        <r>
+          <t>student_id:290ae795-d7c5-481a-80e2-8ccbe70cfd4a</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B23" authorId="0">
+      <text>
+        <r>
+          <t>student_id:3babeede-6ba0-4b46-8f32-8c198e1888c5</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B24" authorId="0">
+      <text>
+        <r>
+          <t>student_id:7fe81e9e-0fef-4c80-a488-b863e8f384f1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B25" authorId="0">
+      <text>
+        <r>
+          <t>student_id:eff7102c-d341-40b6-8733-8249c176a712</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B26" authorId="0">
+      <text>
+        <r>
+          <t>student_id:db343d21-0ae6-4bd7-9301-0394dfcdab1e</t>
         </r>
       </text>
     </comment>
@@ -134,7 +176,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="42">
   <si>
     <t>زهراوي علمي 1  |  AMPHI  |  BAC  |  زهراوي</t>
   </si>
@@ -157,51 +199,57 @@
     <t>الاسم واللقب</t>
   </si>
   <si>
-    <t>10/09/2026</t>
+    <t>01/10/2026</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
+    <t>محروق سيد أحمد</t>
+  </si>
+  <si>
+    <t>فاروقي أنيس+مايا</t>
+  </si>
+  <si>
+    <t>كروش محمد اسلام</t>
+  </si>
+  <si>
+    <t>شبايكي شهد</t>
+  </si>
+  <si>
+    <t>عثماني كريم</t>
+  </si>
+  <si>
+    <t>حمانة ريهام</t>
+  </si>
+  <si>
+    <t>بوشمة أنفال</t>
+  </si>
+  <si>
     <t>بن نيو اياد</t>
   </si>
   <si>
-    <t>فاروقي أنيس+مايا</t>
-  </si>
-  <si>
-    <t>محروق سيد أحمد</t>
-  </si>
-  <si>
     <t>بوبيدي لينا</t>
   </si>
   <si>
+    <t>نايت محند معتز</t>
+  </si>
+  <si>
     <t>حرز الله عبد المجيب</t>
   </si>
   <si>
     <t>بوشامة سارة</t>
   </si>
   <si>
-    <t>حمانة ريهام</t>
-  </si>
-  <si>
-    <t>بوشمة أنفال</t>
-  </si>
-  <si>
-    <t>نايت محند معتز</t>
-  </si>
-  <si>
     <t>زغليش شكيب أرسلان</t>
   </si>
   <si>
-    <t>سعدوني رنيم</t>
+    <t>كحيلي احمد سامي</t>
   </si>
   <si>
     <t>جلواط نسرين</t>
   </si>
   <si>
-    <t>عثماني كريم</t>
-  </si>
-  <si>
     <t>داودي سندس</t>
   </si>
   <si>
@@ -209,6 +257,18 @@
   </si>
   <si>
     <t>علي طالب ادم</t>
+  </si>
+  <si>
+    <t>مؤنس السعيد</t>
+  </si>
+  <si>
+    <t>عبوة هبة</t>
+  </si>
+  <si>
+    <t>خرفوشي عبد المعز</t>
+  </si>
+  <si>
+    <t>ديب عبد الكريم</t>
   </si>
   <si>
     <t>تعليمات ملء الحضور والكتب / Instructions</t>
@@ -728,7 +788,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -853,7 +913,7 @@
     </row>
     <row r="5" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>9</v>
@@ -897,7 +957,7 @@
     </row>
     <row r="6" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>10</v>
@@ -941,7 +1001,7 @@
     </row>
     <row r="7" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>11</v>
@@ -985,7 +1045,7 @@
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>12</v>
@@ -1029,7 +1089,7 @@
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>265</v>
+        <v>166</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>13</v>
@@ -1073,7 +1133,7 @@
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>298</v>
+        <v>173</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>14</v>
@@ -1117,7 +1177,7 @@
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>403</v>
+        <v>174</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>15</v>
@@ -1161,7 +1221,7 @@
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>404</v>
+        <v>175</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>16</v>
@@ -1205,7 +1265,7 @@
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>405</v>
+        <v>176</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>17</v>
@@ -1249,7 +1309,7 @@
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>406</v>
+        <v>177</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>18</v>
@@ -1293,7 +1353,7 @@
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>407</v>
+        <v>178</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>19</v>
@@ -1337,7 +1397,7 @@
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>408</v>
+        <v>179</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>20</v>
@@ -1381,7 +1441,7 @@
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>409</v>
+        <v>180</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>21</v>
@@ -1425,7 +1485,7 @@
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>410</v>
+        <v>181</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>22</v>
@@ -1469,7 +1529,7 @@
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>411</v>
+        <v>182</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>23</v>
@@ -1513,7 +1573,7 @@
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>412</v>
+        <v>183</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>24</v>
@@ -1552,6 +1612,270 @@
         <v>0</v>
       </c>
       <c r="N20" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
+        <v>184</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="8">
+        <v>0</v>
+      </c>
+      <c r="D21" s="8">
+        <v>0</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0</v>
+      </c>
+      <c r="F21" s="8">
+        <v>0</v>
+      </c>
+      <c r="G21" s="8">
+        <v>0</v>
+      </c>
+      <c r="H21" s="8">
+        <v>0</v>
+      </c>
+      <c r="I21" s="8">
+        <v>0</v>
+      </c>
+      <c r="J21" s="8">
+        <v>0</v>
+      </c>
+      <c r="K21" s="8">
+        <v>0</v>
+      </c>
+      <c r="L21" s="8">
+        <v>0</v>
+      </c>
+      <c r="M21" s="8">
+        <v>0</v>
+      </c>
+      <c r="N21" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
+        <v>185</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="9">
+        <v>0</v>
+      </c>
+      <c r="D22" s="9">
+        <v>0</v>
+      </c>
+      <c r="E22" s="9">
+        <v>0</v>
+      </c>
+      <c r="F22" s="9">
+        <v>0</v>
+      </c>
+      <c r="G22" s="9">
+        <v>0</v>
+      </c>
+      <c r="H22" s="9">
+        <v>0</v>
+      </c>
+      <c r="I22" s="9">
+        <v>0</v>
+      </c>
+      <c r="J22" s="9">
+        <v>0</v>
+      </c>
+      <c r="K22" s="9">
+        <v>0</v>
+      </c>
+      <c r="L22" s="9">
+        <v>0</v>
+      </c>
+      <c r="M22" s="9">
+        <v>0</v>
+      </c>
+      <c r="N22" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="6">
+        <v>186</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="8">
+        <v>0</v>
+      </c>
+      <c r="D23" s="8">
+        <v>0</v>
+      </c>
+      <c r="E23" s="8">
+        <v>0</v>
+      </c>
+      <c r="F23" s="8">
+        <v>0</v>
+      </c>
+      <c r="G23" s="8">
+        <v>0</v>
+      </c>
+      <c r="H23" s="8">
+        <v>0</v>
+      </c>
+      <c r="I23" s="8">
+        <v>0</v>
+      </c>
+      <c r="J23" s="8">
+        <v>0</v>
+      </c>
+      <c r="K23" s="8">
+        <v>0</v>
+      </c>
+      <c r="L23" s="8">
+        <v>0</v>
+      </c>
+      <c r="M23" s="8">
+        <v>0</v>
+      </c>
+      <c r="N23" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
+        <v>187</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="9">
+        <v>0</v>
+      </c>
+      <c r="D24" s="9">
+        <v>0</v>
+      </c>
+      <c r="E24" s="9">
+        <v>0</v>
+      </c>
+      <c r="F24" s="9">
+        <v>0</v>
+      </c>
+      <c r="G24" s="9">
+        <v>0</v>
+      </c>
+      <c r="H24" s="9">
+        <v>0</v>
+      </c>
+      <c r="I24" s="9">
+        <v>0</v>
+      </c>
+      <c r="J24" s="9">
+        <v>0</v>
+      </c>
+      <c r="K24" s="9">
+        <v>0</v>
+      </c>
+      <c r="L24" s="9">
+        <v>0</v>
+      </c>
+      <c r="M24" s="9">
+        <v>0</v>
+      </c>
+      <c r="N24" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="6">
+        <v>188</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="8">
+        <v>0</v>
+      </c>
+      <c r="D25" s="8">
+        <v>0</v>
+      </c>
+      <c r="E25" s="8">
+        <v>0</v>
+      </c>
+      <c r="F25" s="8">
+        <v>0</v>
+      </c>
+      <c r="G25" s="8">
+        <v>0</v>
+      </c>
+      <c r="H25" s="8">
+        <v>0</v>
+      </c>
+      <c r="I25" s="8">
+        <v>0</v>
+      </c>
+      <c r="J25" s="8">
+        <v>0</v>
+      </c>
+      <c r="K25" s="8">
+        <v>0</v>
+      </c>
+      <c r="L25" s="8">
+        <v>0</v>
+      </c>
+      <c r="M25" s="8">
+        <v>0</v>
+      </c>
+      <c r="N25" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="6">
+        <v>189</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="9">
+        <v>0</v>
+      </c>
+      <c r="D26" s="9">
+        <v>0</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0</v>
+      </c>
+      <c r="F26" s="9">
+        <v>0</v>
+      </c>
+      <c r="G26" s="9">
+        <v>0</v>
+      </c>
+      <c r="H26" s="9">
+        <v>0</v>
+      </c>
+      <c r="I26" s="9">
+        <v>0</v>
+      </c>
+      <c r="J26" s="9">
+        <v>0</v>
+      </c>
+      <c r="K26" s="9">
+        <v>0</v>
+      </c>
+      <c r="L26" s="9">
+        <v>0</v>
+      </c>
+      <c r="M26" s="9">
+        <v>0</v>
+      </c>
+      <c r="N26" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1579,7 +1903,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -1589,12 +1913,12 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
@@ -1604,27 +1928,27 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -1634,12 +1958,12 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
@@ -1649,7 +1973,7 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/data/attendance/AMPHI_زهراوي_علمي_1.xlsx
+++ b/data/attendance/AMPHI_زهراوي_علمي_1.xlsx
@@ -34,140 +34,231 @@
     <comment ref="B7" authorId="0">
       <text>
         <r>
+          <t>student_id:7a2c6860-ac25-4bf1-9c59-b40318e03d3b</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B8" authorId="0">
+      <text>
+        <r>
           <t>student_id:62f8dbea-d839-4620-852b-c61095b6129a</t>
         </r>
       </text>
     </comment>
-    <comment ref="B8" authorId="0">
+    <comment ref="B9" authorId="0">
+      <text>
+        <r>
+          <t>student_id:d8da6d91-e82a-403d-be1c-7379d8f3f360</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B10" authorId="0">
+      <text>
+        <r>
+          <t>student_id:b5434f48-2bed-43a0-ada7-62bd10b64a5e</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B11" authorId="0">
+      <text>
+        <r>
+          <t>student_id:4d5d15c8-b6af-497d-8dc9-cd3ac6a818a0</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B12" authorId="0">
+      <text>
+        <r>
+          <t>student_id:b2aa80de-d2f9-47f9-9e3d-e8aaabe829e7</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B13" authorId="0">
       <text>
         <r>
           <t>student_id:a9f2b729-1881-4aa9-8b7f-c010c77d6ff9</t>
         </r>
       </text>
     </comment>
-    <comment ref="B9" authorId="0">
+    <comment ref="B14" authorId="0">
       <text>
         <r>
           <t>student_id:f9665799-bcdd-42cb-9ee2-2c0b46fad4a7</t>
         </r>
       </text>
     </comment>
-    <comment ref="B10" authorId="0">
+    <comment ref="B15" authorId="0">
       <text>
         <r>
           <t>student_id:beb5a9b5-ace2-4d8c-8fa8-13d95aaf14b2</t>
         </r>
       </text>
     </comment>
-    <comment ref="B11" authorId="0">
+    <comment ref="B16" authorId="0">
       <text>
         <r>
           <t>student_id:9b9aff36-6a0b-434b-ad5d-59c60712d22b</t>
         </r>
       </text>
     </comment>
-    <comment ref="B12" authorId="0">
+    <comment ref="B17" authorId="0">
       <text>
         <r>
           <t>student_id:30e3101c-0da1-45b4-ac64-04627e553de6</t>
         </r>
       </text>
     </comment>
-    <comment ref="B13" authorId="0">
+    <comment ref="B18" authorId="0">
       <text>
         <r>
           <t>student_id:9480e9ce-8e6d-4576-81ec-49d56fd56037</t>
         </r>
       </text>
     </comment>
-    <comment ref="B14" authorId="0">
+    <comment ref="B19" authorId="0">
       <text>
         <r>
           <t>student_id:5c4e15c8-f573-4322-ad01-86920db813a5</t>
         </r>
       </text>
     </comment>
-    <comment ref="B15" authorId="0">
+    <comment ref="B20" authorId="0">
       <text>
         <r>
           <t>student_id:74d856fa-0759-40be-8901-05a9e9c0add7</t>
         </r>
       </text>
     </comment>
-    <comment ref="B16" authorId="0">
+    <comment ref="B21" authorId="0">
       <text>
         <r>
           <t>student_id:2a443aed-c07a-4324-9e86-72a882fc64a8</t>
         </r>
       </text>
     </comment>
-    <comment ref="B17" authorId="0">
+    <comment ref="B22" authorId="0">
       <text>
         <r>
           <t>student_id:069184e6-7edb-4d5d-b591-5b660f8d0159</t>
         </r>
       </text>
     </comment>
-    <comment ref="B18" authorId="0">
+    <comment ref="B23" authorId="0">
       <text>
         <r>
           <t>student_id:e37c1325-4b0d-41a1-918b-2622eac4a0da</t>
         </r>
       </text>
     </comment>
-    <comment ref="B19" authorId="0">
+    <comment ref="B24" authorId="0">
       <text>
         <r>
           <t>student_id:4c2f9380-3065-42fe-852f-ac7919272b9a</t>
         </r>
       </text>
     </comment>
-    <comment ref="B20" authorId="0">
+    <comment ref="B25" authorId="0">
       <text>
         <r>
           <t>student_id:4578980d-ce40-4241-a7f9-008902aa677c</t>
         </r>
       </text>
     </comment>
-    <comment ref="B21" authorId="0">
+    <comment ref="B26" authorId="0">
       <text>
         <r>
           <t>student_id:3190f13f-dec8-40a7-9922-9bad9efee130</t>
         </r>
       </text>
     </comment>
-    <comment ref="B22" authorId="0">
+    <comment ref="B27" authorId="0">
       <text>
         <r>
           <t>student_id:290ae795-d7c5-481a-80e2-8ccbe70cfd4a</t>
         </r>
       </text>
     </comment>
-    <comment ref="B23" authorId="0">
+    <comment ref="B28" authorId="0">
       <text>
         <r>
           <t>student_id:3babeede-6ba0-4b46-8f32-8c198e1888c5</t>
         </r>
       </text>
     </comment>
-    <comment ref="B24" authorId="0">
+    <comment ref="B29" authorId="0">
       <text>
         <r>
           <t>student_id:7fe81e9e-0fef-4c80-a488-b863e8f384f1</t>
         </r>
       </text>
     </comment>
-    <comment ref="B25" authorId="0">
+    <comment ref="B30" authorId="0">
       <text>
         <r>
           <t>student_id:eff7102c-d341-40b6-8733-8249c176a712</t>
         </r>
       </text>
     </comment>
-    <comment ref="B26" authorId="0">
+    <comment ref="B31" authorId="0">
       <text>
         <r>
           <t>student_id:db343d21-0ae6-4bd7-9301-0394dfcdab1e</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B32" authorId="0">
+      <text>
+        <r>
+          <t>student_id:25dc1361-b288-44d8-8f62-9d715d6e5282</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B33" authorId="0">
+      <text>
+        <r>
+          <t>student_id:bfb87398-0134-4c04-bd8f-02efbc011e7b</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B34" authorId="0">
+      <text>
+        <r>
+          <t>student_id:6d5b9fd4-bf2c-41d7-b425-cfb888b17ca6</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B35" authorId="0">
+      <text>
+        <r>
+          <t>student_id:c2395d0c-0ddf-48e0-9093-a838b6054764</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B36" authorId="0">
+      <text>
+        <r>
+          <t>student_id:7802264c-2dd3-43de-addb-f9c062946825</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B37" authorId="0">
+      <text>
+        <r>
+          <t>student_id:634f91a0-f7b3-4981-be1e-e3cc521b1464</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B38" authorId="0">
+      <text>
+        <r>
+          <t>student_id:ba54c276-ecef-45ad-ab87-1e1766ed57b6</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B39" authorId="0">
+      <text>
+        <r>
+          <t>student_id:4709724b-9f36-4d1d-b582-73bd2ddf2079</t>
         </r>
       </text>
     </comment>
@@ -176,7 +267,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="57">
   <si>
     <t>زهراوي علمي 1  |  AMPHI  |  BAC  |  زهراوي</t>
   </si>
@@ -190,6 +281,9 @@
     <t>has_books=false</t>
   </si>
   <si>
+    <t>is_formation=false</t>
+  </si>
+  <si>
     <t>حصة مجانية؟ (1 = نعم / 0 = عادية)</t>
   </si>
   <si>
@@ -211,9 +305,24 @@
     <t>فاروقي أنيس+مايا</t>
   </si>
   <si>
+    <t>خليفي رفيدة</t>
+  </si>
+  <si>
     <t>كروش محمد اسلام</t>
   </si>
   <si>
+    <t>بلبعلي ندى</t>
+  </si>
+  <si>
+    <t>غربي جمانة</t>
+  </si>
+  <si>
+    <t>ليتيم مليسا</t>
+  </si>
+  <si>
+    <t>نحال لينا</t>
+  </si>
+  <si>
     <t>شبايكي شهد</t>
   </si>
   <si>
@@ -271,6 +380,30 @@
     <t>ديب عبد الكريم</t>
   </si>
   <si>
+    <t>زرقين يحيى</t>
+  </si>
+  <si>
+    <t>سعدي رنيم</t>
+  </si>
+  <si>
+    <t>طويل ميسون</t>
+  </si>
+  <si>
+    <t>اقيس لجين</t>
+  </si>
+  <si>
+    <t>بن احمد ميساء</t>
+  </si>
+  <si>
+    <t>فنيخ شهد رشا</t>
+  </si>
+  <si>
+    <t>عبد المؤمن دانية اسراء</t>
+  </si>
+  <si>
+    <t>هواري امنية ياسمين</t>
+  </si>
+  <si>
     <t>تعليمات ملء الحضور والكتب / Instructions</t>
   </si>
   <si>
@@ -298,7 +431,10 @@
     <t>3. للأفواج التي لها كتب (ت1 / ت2 / ت3) :</t>
   </si>
   <si>
-    <t xml:space="preserve">   → اكتب 1 في خانة الفصل إذا استلم الطالب كتابه، أو 0 إذا لم يستلم</t>
+    <t xml:space="preserve">   → للأفواج التي لها كتابان في هذا الفصل (ت1): تم توفير عمودين (كتاب 1 ت 1 و كتاب 2 ت 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   → اكتب 1 (أو X) في خانة الكتاب إذا استلم الطالب نسخته، أو 0 إذا لم يستلم</t>
   </si>
   <si>
     <t>4. احفظ الملف (Ctrl+S) بعد الانتهاء ثم شغّل أمر الاستيراد.</t>
@@ -788,7 +924,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -814,7 +950,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" hidden="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" hidden="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -824,10 +960,13 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="3">
@@ -869,46 +1008,46 @@
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -916,7 +1055,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" s="8">
         <v>0</v>
@@ -960,7 +1099,7 @@
         <v>31</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="9">
         <v>0</v>
@@ -1001,10 +1140,10 @@
     </row>
     <row r="7" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" s="8">
         <v>0</v>
@@ -1045,10 +1184,10 @@
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>161</v>
+        <v>82</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" s="9">
         <v>0</v>
@@ -1089,10 +1228,10 @@
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" s="8">
         <v>0</v>
@@ -1133,10 +1272,10 @@
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>173</v>
+        <v>126</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" s="9">
         <v>0</v>
@@ -1177,10 +1316,10 @@
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" s="8">
         <v>0</v>
@@ -1221,10 +1360,10 @@
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>175</v>
+        <v>144</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" s="9">
         <v>0</v>
@@ -1265,10 +1404,10 @@
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" s="8">
         <v>0</v>
@@ -1309,10 +1448,10 @@
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" s="9">
         <v>0</v>
@@ -1353,10 +1492,10 @@
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15" s="8">
         <v>0</v>
@@ -1397,10 +1536,10 @@
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C16" s="9">
         <v>0</v>
@@ -1441,10 +1580,10 @@
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C17" s="8">
         <v>0</v>
@@ -1485,10 +1624,10 @@
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" s="9">
         <v>0</v>
@@ -1529,10 +1668,10 @@
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C19" s="8">
         <v>0</v>
@@ -1573,10 +1712,10 @@
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C20" s="9">
         <v>0</v>
@@ -1617,10 +1756,10 @@
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C21" s="8">
         <v>0</v>
@@ -1661,10 +1800,10 @@
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" s="9">
         <v>0</v>
@@ -1705,10 +1844,10 @@
     </row>
     <row r="23" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C23" s="8">
         <v>0</v>
@@ -1749,10 +1888,10 @@
     </row>
     <row r="24" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C24" s="9">
         <v>0</v>
@@ -1793,10 +1932,10 @@
     </row>
     <row r="25" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C25" s="8">
         <v>0</v>
@@ -1837,45 +1976,617 @@
     </row>
     <row r="26" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
+        <v>184</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="9">
+        <v>0</v>
+      </c>
+      <c r="D26" s="9">
+        <v>0</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0</v>
+      </c>
+      <c r="F26" s="9">
+        <v>0</v>
+      </c>
+      <c r="G26" s="9">
+        <v>0</v>
+      </c>
+      <c r="H26" s="9">
+        <v>0</v>
+      </c>
+      <c r="I26" s="9">
+        <v>0</v>
+      </c>
+      <c r="J26" s="9">
+        <v>0</v>
+      </c>
+      <c r="K26" s="9">
+        <v>0</v>
+      </c>
+      <c r="L26" s="9">
+        <v>0</v>
+      </c>
+      <c r="M26" s="9">
+        <v>0</v>
+      </c>
+      <c r="N26" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="6">
+        <v>185</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="8">
+        <v>0</v>
+      </c>
+      <c r="D27" s="8">
+        <v>0</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0</v>
+      </c>
+      <c r="F27" s="8">
+        <v>0</v>
+      </c>
+      <c r="G27" s="8">
+        <v>0</v>
+      </c>
+      <c r="H27" s="8">
+        <v>0</v>
+      </c>
+      <c r="I27" s="8">
+        <v>0</v>
+      </c>
+      <c r="J27" s="8">
+        <v>0</v>
+      </c>
+      <c r="K27" s="8">
+        <v>0</v>
+      </c>
+      <c r="L27" s="8">
+        <v>0</v>
+      </c>
+      <c r="M27" s="8">
+        <v>0</v>
+      </c>
+      <c r="N27" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="6">
+        <v>186</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" s="9">
+        <v>0</v>
+      </c>
+      <c r="D28" s="9">
+        <v>0</v>
+      </c>
+      <c r="E28" s="9">
+        <v>0</v>
+      </c>
+      <c r="F28" s="9">
+        <v>0</v>
+      </c>
+      <c r="G28" s="9">
+        <v>0</v>
+      </c>
+      <c r="H28" s="9">
+        <v>0</v>
+      </c>
+      <c r="I28" s="9">
+        <v>0</v>
+      </c>
+      <c r="J28" s="9">
+        <v>0</v>
+      </c>
+      <c r="K28" s="9">
+        <v>0</v>
+      </c>
+      <c r="L28" s="9">
+        <v>0</v>
+      </c>
+      <c r="M28" s="9">
+        <v>0</v>
+      </c>
+      <c r="N28" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="6">
+        <v>187</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="8">
+        <v>0</v>
+      </c>
+      <c r="D29" s="8">
+        <v>0</v>
+      </c>
+      <c r="E29" s="8">
+        <v>0</v>
+      </c>
+      <c r="F29" s="8">
+        <v>0</v>
+      </c>
+      <c r="G29" s="8">
+        <v>0</v>
+      </c>
+      <c r="H29" s="8">
+        <v>0</v>
+      </c>
+      <c r="I29" s="8">
+        <v>0</v>
+      </c>
+      <c r="J29" s="8">
+        <v>0</v>
+      </c>
+      <c r="K29" s="8">
+        <v>0</v>
+      </c>
+      <c r="L29" s="8">
+        <v>0</v>
+      </c>
+      <c r="M29" s="8">
+        <v>0</v>
+      </c>
+      <c r="N29" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
+        <v>188</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="9">
+        <v>0</v>
+      </c>
+      <c r="D30" s="9">
+        <v>0</v>
+      </c>
+      <c r="E30" s="9">
+        <v>0</v>
+      </c>
+      <c r="F30" s="9">
+        <v>0</v>
+      </c>
+      <c r="G30" s="9">
+        <v>0</v>
+      </c>
+      <c r="H30" s="9">
+        <v>0</v>
+      </c>
+      <c r="I30" s="9">
+        <v>0</v>
+      </c>
+      <c r="J30" s="9">
+        <v>0</v>
+      </c>
+      <c r="K30" s="9">
+        <v>0</v>
+      </c>
+      <c r="L30" s="9">
+        <v>0</v>
+      </c>
+      <c r="M30" s="9">
+        <v>0</v>
+      </c>
+      <c r="N30" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
         <v>189</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" s="9">
-        <v>0</v>
-      </c>
-      <c r="D26" s="9">
-        <v>0</v>
-      </c>
-      <c r="E26" s="9">
-        <v>0</v>
-      </c>
-      <c r="F26" s="9">
-        <v>0</v>
-      </c>
-      <c r="G26" s="9">
-        <v>0</v>
-      </c>
-      <c r="H26" s="9">
-        <v>0</v>
-      </c>
-      <c r="I26" s="9">
-        <v>0</v>
-      </c>
-      <c r="J26" s="9">
-        <v>0</v>
-      </c>
-      <c r="K26" s="9">
-        <v>0</v>
-      </c>
-      <c r="L26" s="9">
-        <v>0</v>
-      </c>
-      <c r="M26" s="9">
-        <v>0</v>
-      </c>
-      <c r="N26" s="9">
+      <c r="B31" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="8">
+        <v>0</v>
+      </c>
+      <c r="D31" s="8">
+        <v>0</v>
+      </c>
+      <c r="E31" s="8">
+        <v>0</v>
+      </c>
+      <c r="F31" s="8">
+        <v>0</v>
+      </c>
+      <c r="G31" s="8">
+        <v>0</v>
+      </c>
+      <c r="H31" s="8">
+        <v>0</v>
+      </c>
+      <c r="I31" s="8">
+        <v>0</v>
+      </c>
+      <c r="J31" s="8">
+        <v>0</v>
+      </c>
+      <c r="K31" s="8">
+        <v>0</v>
+      </c>
+      <c r="L31" s="8">
+        <v>0</v>
+      </c>
+      <c r="M31" s="8">
+        <v>0</v>
+      </c>
+      <c r="N31" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="6">
+        <v>612</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="9">
+        <v>0</v>
+      </c>
+      <c r="D32" s="9">
+        <v>0</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0</v>
+      </c>
+      <c r="F32" s="9">
+        <v>0</v>
+      </c>
+      <c r="G32" s="9">
+        <v>0</v>
+      </c>
+      <c r="H32" s="9">
+        <v>0</v>
+      </c>
+      <c r="I32" s="9">
+        <v>0</v>
+      </c>
+      <c r="J32" s="9">
+        <v>0</v>
+      </c>
+      <c r="K32" s="9">
+        <v>0</v>
+      </c>
+      <c r="L32" s="9">
+        <v>0</v>
+      </c>
+      <c r="M32" s="9">
+        <v>0</v>
+      </c>
+      <c r="N32" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="6">
+        <v>679</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" s="8">
+        <v>0</v>
+      </c>
+      <c r="D33" s="8">
+        <v>0</v>
+      </c>
+      <c r="E33" s="8">
+        <v>0</v>
+      </c>
+      <c r="F33" s="8">
+        <v>0</v>
+      </c>
+      <c r="G33" s="8">
+        <v>0</v>
+      </c>
+      <c r="H33" s="8">
+        <v>0</v>
+      </c>
+      <c r="I33" s="8">
+        <v>0</v>
+      </c>
+      <c r="J33" s="8">
+        <v>0</v>
+      </c>
+      <c r="K33" s="8">
+        <v>0</v>
+      </c>
+      <c r="L33" s="8">
+        <v>0</v>
+      </c>
+      <c r="M33" s="8">
+        <v>0</v>
+      </c>
+      <c r="N33" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="6">
+        <v>706</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" s="9">
+        <v>0</v>
+      </c>
+      <c r="D34" s="9">
+        <v>0</v>
+      </c>
+      <c r="E34" s="9">
+        <v>0</v>
+      </c>
+      <c r="F34" s="9">
+        <v>0</v>
+      </c>
+      <c r="G34" s="9">
+        <v>0</v>
+      </c>
+      <c r="H34" s="9">
+        <v>0</v>
+      </c>
+      <c r="I34" s="9">
+        <v>0</v>
+      </c>
+      <c r="J34" s="9">
+        <v>0</v>
+      </c>
+      <c r="K34" s="9">
+        <v>0</v>
+      </c>
+      <c r="L34" s="9">
+        <v>0</v>
+      </c>
+      <c r="M34" s="9">
+        <v>0</v>
+      </c>
+      <c r="N34" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="6">
+        <v>829</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" s="8">
+        <v>0</v>
+      </c>
+      <c r="D35" s="8">
+        <v>0</v>
+      </c>
+      <c r="E35" s="8">
+        <v>0</v>
+      </c>
+      <c r="F35" s="8">
+        <v>0</v>
+      </c>
+      <c r="G35" s="8">
+        <v>0</v>
+      </c>
+      <c r="H35" s="8">
+        <v>0</v>
+      </c>
+      <c r="I35" s="8">
+        <v>0</v>
+      </c>
+      <c r="J35" s="8">
+        <v>0</v>
+      </c>
+      <c r="K35" s="8">
+        <v>0</v>
+      </c>
+      <c r="L35" s="8">
+        <v>0</v>
+      </c>
+      <c r="M35" s="8">
+        <v>0</v>
+      </c>
+      <c r="N35" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="6">
+        <v>830</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" s="9">
+        <v>0</v>
+      </c>
+      <c r="D36" s="9">
+        <v>0</v>
+      </c>
+      <c r="E36" s="9">
+        <v>0</v>
+      </c>
+      <c r="F36" s="9">
+        <v>0</v>
+      </c>
+      <c r="G36" s="9">
+        <v>0</v>
+      </c>
+      <c r="H36" s="9">
+        <v>0</v>
+      </c>
+      <c r="I36" s="9">
+        <v>0</v>
+      </c>
+      <c r="J36" s="9">
+        <v>0</v>
+      </c>
+      <c r="K36" s="9">
+        <v>0</v>
+      </c>
+      <c r="L36" s="9">
+        <v>0</v>
+      </c>
+      <c r="M36" s="9">
+        <v>0</v>
+      </c>
+      <c r="N36" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" s="6">
+        <v>831</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" s="8">
+        <v>0</v>
+      </c>
+      <c r="D37" s="8">
+        <v>0</v>
+      </c>
+      <c r="E37" s="8">
+        <v>0</v>
+      </c>
+      <c r="F37" s="8">
+        <v>0</v>
+      </c>
+      <c r="G37" s="8">
+        <v>0</v>
+      </c>
+      <c r="H37" s="8">
+        <v>0</v>
+      </c>
+      <c r="I37" s="8">
+        <v>0</v>
+      </c>
+      <c r="J37" s="8">
+        <v>0</v>
+      </c>
+      <c r="K37" s="8">
+        <v>0</v>
+      </c>
+      <c r="L37" s="8">
+        <v>0</v>
+      </c>
+      <c r="M37" s="8">
+        <v>0</v>
+      </c>
+      <c r="N37" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" s="6">
+        <v>832</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C38" s="9">
+        <v>0</v>
+      </c>
+      <c r="D38" s="9">
+        <v>0</v>
+      </c>
+      <c r="E38" s="9">
+        <v>0</v>
+      </c>
+      <c r="F38" s="9">
+        <v>0</v>
+      </c>
+      <c r="G38" s="9">
+        <v>0</v>
+      </c>
+      <c r="H38" s="9">
+        <v>0</v>
+      </c>
+      <c r="I38" s="9">
+        <v>0</v>
+      </c>
+      <c r="J38" s="9">
+        <v>0</v>
+      </c>
+      <c r="K38" s="9">
+        <v>0</v>
+      </c>
+      <c r="L38" s="9">
+        <v>0</v>
+      </c>
+      <c r="M38" s="9">
+        <v>0</v>
+      </c>
+      <c r="N38" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
+        <v>833</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C39" s="8">
+        <v>0</v>
+      </c>
+      <c r="D39" s="8">
+        <v>0</v>
+      </c>
+      <c r="E39" s="8">
+        <v>0</v>
+      </c>
+      <c r="F39" s="8">
+        <v>0</v>
+      </c>
+      <c r="G39" s="8">
+        <v>0</v>
+      </c>
+      <c r="H39" s="8">
+        <v>0</v>
+      </c>
+      <c r="I39" s="8">
+        <v>0</v>
+      </c>
+      <c r="J39" s="8">
+        <v>0</v>
+      </c>
+      <c r="K39" s="8">
+        <v>0</v>
+      </c>
+      <c r="L39" s="8">
+        <v>0</v>
+      </c>
+      <c r="M39" s="8">
+        <v>0</v>
+      </c>
+      <c r="N39" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1895,7 +2606,7 @@
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
@@ -1903,77 +2614,82 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
